--- a/exports/trend_1d/ADANIENT_full_report.xlsx
+++ b/exports/trend_1d/ADANIENT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>12.5</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42075</v>
+        <v>42076</v>
       </c>
       <c r="H2" t="n">
-        <v>188.6</v>
+        <v>182.4</v>
       </c>
       <c r="I2" t="n">
         <v>183.7378145633836</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K2" t="n">
-        <v>30.88</v>
+        <v>26.58</v>
       </c>
       <c r="L2" t="n">
         <v>2.98</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.68</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42104</v>
+        <v>42107</v>
       </c>
       <c r="H3" t="n">
-        <v>183.5</v>
+        <v>190.4</v>
       </c>
       <c r="I3" t="n">
         <v>189.7178952085906</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6</v>
+        <v>-4.39</v>
       </c>
       <c r="L3" t="n">
         <v>4.88</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.3</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H4" t="n">
-        <v>211.3</v>
+        <v>203.2</v>
       </c>
       <c r="I4" t="n">
         <v>206.8244078098456</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K4" t="n">
-        <v>10.98</v>
+        <v>6.72</v>
       </c>
       <c r="L4" t="n">
         <v>4.52</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.49</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42219</v>
+        <v>42220</v>
       </c>
       <c r="H5" t="n">
-        <v>82.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>89.16653712921165</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K5" t="n">
-        <v>59.55</v>
+        <v>54.92</v>
       </c>
       <c r="L5" t="n">
         <v>173.52</v>
@@ -726,7 +785,7 @@
         <v>203.38</v>
       </c>
       <c r="N5" t="n">
-        <v>8.32</v>
+        <v>11.44</v>
       </c>
       <c r="O5" t="n">
         <v>-3.83</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>19.41</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42235</v>
+        <v>42236</v>
       </c>
       <c r="H6" t="n">
-        <v>83.2</v>
+        <v>80.7</v>
       </c>
       <c r="I6" t="n">
         <v>81.2912534905718</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.17</v>
+        <v>-11.9</v>
       </c>
       <c r="L6" t="n">
-        <v>10.59</v>
+        <v>12.99</v>
       </c>
       <c r="M6" t="n">
         <v>1.46</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>20.3</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42282</v>
+        <v>42283</v>
       </c>
       <c r="H7" t="n">
-        <v>79.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>79.7677013082687</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K7" t="n">
-        <v>1.24</v>
+        <v>-1.12</v>
       </c>
       <c r="L7" t="n">
         <v>6.69</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>14.85</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42312</v>
+        <v>42313</v>
       </c>
       <c r="H8" t="n">
-        <v>82.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>80.80054632904989</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>1.23</v>
+        <v>-3.06</v>
       </c>
       <c r="L8" t="n">
-        <v>2.33</v>
+        <v>3.8</v>
       </c>
       <c r="M8" t="n">
         <v>0.64</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>16.55</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42361</v>
+        <v>42362</v>
       </c>
       <c r="H9" t="n">
-        <v>79.8</v>
+        <v>81.7</v>
       </c>
       <c r="I9" t="n">
         <v>81.19126035623444</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.88</v>
+        <v>-3.29</v>
       </c>
       <c r="L9" t="n">
         <v>4.42</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>12.47</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H10" t="n">
-        <v>75.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>74.47517528794562</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.71</v>
+        <v>-11.75</v>
       </c>
       <c r="L10" t="n">
-        <v>8.449999999999999</v>
+        <v>12.36</v>
       </c>
       <c r="M10" t="n">
         <v>2.42</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>22.42</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42451</v>
+        <v>42452</v>
       </c>
       <c r="H11" t="n">
-        <v>66.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="I11" t="n">
         <v>67.60674470842531</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K11" t="n">
-        <v>7.91</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
         <v>7.35</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.55</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42495</v>
+        <v>42496</v>
       </c>
       <c r="H12" t="n">
-        <v>75.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>74.6748313293989</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K12" t="n">
-        <v>9.710000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="L12" t="n">
         <v>5.8</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>14.73</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42535</v>
+        <v>42536</v>
       </c>
       <c r="H13" t="n">
-        <v>76.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="I13" t="n">
         <v>77.42767311698078</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.69</v>
+        <v>-4.17</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="M13" t="n">
         <v>1.23</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.82</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42584</v>
+        <v>42585</v>
       </c>
       <c r="H14" t="n">
-        <v>75.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>72.95464648491757</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.71</v>
+        <v>-5.94</v>
       </c>
       <c r="L14" t="n">
         <v>9.550000000000001</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>14.68</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42706</v>
+        <v>42709</v>
       </c>
       <c r="H15" t="n">
-        <v>66</v>
+        <v>67.5</v>
       </c>
       <c r="I15" t="n">
         <v>66.16435302756322</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K15" t="n">
-        <v>9.470000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="L15" t="n">
         <v>8.23</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>12.94</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42850</v>
+        <v>42851</v>
       </c>
       <c r="H16" t="n">
-        <v>145.4</v>
+        <v>114.9</v>
       </c>
       <c r="I16" t="n">
         <v>122.4957166767174</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K16" t="n">
-        <v>115.41</v>
+        <v>70.22</v>
       </c>
       <c r="L16" t="n">
         <v>3.56</v>
@@ -1353,7 +1544,7 @@
         <v>2.3</v>
       </c>
       <c r="N16" t="n">
-        <v>5.7</v>
+        <v>20.98</v>
       </c>
       <c r="O16" t="n">
         <v>2.27</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>40.87</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42894</v>
+        <v>42895</v>
       </c>
       <c r="H17" t="n">
-        <v>125.8</v>
+        <v>128.2</v>
       </c>
       <c r="I17" t="n">
         <v>128.0026118107971</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.49</v>
+        <v>-11.58</v>
       </c>
       <c r="L17" t="n">
         <v>27.85</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>15.75</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42955</v>
+        <v>42956</v>
       </c>
       <c r="H18" t="n">
-        <v>133.2</v>
+        <v>120.5</v>
       </c>
       <c r="I18" t="n">
         <v>127.1253803370042</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K18" t="n">
-        <v>3.9</v>
+        <v>-6.01</v>
       </c>
       <c r="L18" t="n">
-        <v>6.08</v>
+        <v>8.74</v>
       </c>
       <c r="M18" t="n">
         <v>1.34</v>
       </c>
       <c r="N18" t="n">
-        <v>3.47</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="O18" t="n">
         <v>1.91</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>16.21</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42976</v>
+        <v>42977</v>
       </c>
       <c r="H19" t="n">
-        <v>115.3</v>
+        <v>124.2</v>
       </c>
       <c r="I19" t="n">
         <v>120.8231052898453</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>4.32</v>
+        <v>-3.07</v>
       </c>
       <c r="L19" t="n">
         <v>10.21</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>17.4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H20" t="n">
-        <v>118</v>
+        <v>113.1</v>
       </c>
       <c r="I20" t="n">
         <v>113.5927562263658</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.99</v>
+        <v>-8.94</v>
       </c>
       <c r="L20" t="n">
-        <v>6.2</v>
+        <v>11.19</v>
       </c>
       <c r="M20" t="n">
         <v>2.25</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>14.35</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43033</v>
+        <v>43034</v>
       </c>
       <c r="H21" t="n">
-        <v>123.8</v>
+        <v>127</v>
       </c>
       <c r="I21" t="n">
         <v>124.7400718827736</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K21" t="n">
-        <v>-9.460000000000001</v>
+        <v>-12.29</v>
       </c>
       <c r="L21" t="n">
-        <v>11.23</v>
+        <v>12.91</v>
       </c>
       <c r="M21" t="n">
         <v>3.03</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>12.32</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43164</v>
+        <v>43165</v>
       </c>
       <c r="H22" t="n">
-        <v>194.8</v>
+        <v>180.5</v>
       </c>
       <c r="I22" t="n">
         <v>181.4804977038436</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K22" t="n">
-        <v>53.39</v>
+        <v>42.13</v>
       </c>
       <c r="L22" t="n">
         <v>3.7</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>18.86</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43264</v>
+        <v>43265</v>
       </c>
       <c r="H23" t="n">
-        <v>125.2</v>
+        <v>129.9</v>
       </c>
       <c r="I23" t="n">
         <v>128.8353495802261</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K23" t="n">
-        <v>30.64</v>
+        <v>28.03</v>
       </c>
       <c r="L23" t="n">
         <v>9.199999999999999</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>15.47</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H24" t="n">
-        <v>125.2</v>
+        <v>111.6</v>
       </c>
       <c r="I24" t="n">
         <v>113.0465683533254</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.62</v>
+        <v>-14.09</v>
       </c>
       <c r="L24" t="n">
-        <v>6.54</v>
+        <v>16.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.38</v>
       </c>
       <c r="N24" t="n">
-        <v>3.38</v>
+        <v>10.86</v>
       </c>
       <c r="O24" t="n">
         <v>3.75</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>21.22</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43293</v>
+        <v>43294</v>
       </c>
       <c r="H25" t="n">
-        <v>120.5</v>
+        <v>127.6</v>
       </c>
       <c r="I25" t="n">
         <v>121.4523326094083</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.97</v>
+        <v>-14.34</v>
       </c>
       <c r="L25" t="n">
-        <v>11.2</v>
+        <v>14.87</v>
       </c>
       <c r="M25" t="n">
         <v>1.29</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>19.02</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43348</v>
+        <v>43349</v>
       </c>
       <c r="H26" t="n">
-        <v>204.5</v>
+        <v>158.7</v>
       </c>
       <c r="I26" t="n">
         <v>187.5737162731845</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K26" t="n">
-        <v>60.27</v>
+        <v>24.37</v>
       </c>
       <c r="L26" t="n">
         <v>7.05</v>
       </c>
       <c r="M26" t="n">
-        <v>4.23</v>
+        <v>28.9</v>
       </c>
       <c r="N26" t="n">
-        <v>6.55</v>
+        <v>22.4</v>
       </c>
       <c r="O26" t="n">
         <v>5.89</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>28.13</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43390</v>
+        <v>43392</v>
       </c>
       <c r="H27" t="n">
-        <v>156.8</v>
+        <v>163.6</v>
       </c>
       <c r="I27" t="n">
         <v>159.8640174347291</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K27" t="n">
-        <v>1.2</v>
+        <v>-3.09</v>
       </c>
       <c r="L27" t="n">
-        <v>4.22</v>
+        <v>4.28</v>
       </c>
       <c r="M27" t="n">
         <v>2.17</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>21.68</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43441</v>
+        <v>43444</v>
       </c>
       <c r="H28" t="n">
-        <v>148.2</v>
+        <v>138.8</v>
       </c>
       <c r="I28" t="n">
         <v>144.6616723835656</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K28" t="n">
-        <v>-9.41</v>
+        <v>-15.16</v>
       </c>
       <c r="L28" t="n">
-        <v>11.25</v>
+        <v>16.44</v>
       </c>
       <c r="M28" t="n">
-        <v>1.98</v>
+        <v>3.91</v>
       </c>
       <c r="N28" t="n">
-        <v>4.33</v>
+        <v>6.34</v>
       </c>
       <c r="O28" t="n">
         <v>4.34</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>16.91</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H29" t="n">
-        <v>129.8</v>
+        <v>137.5</v>
       </c>
       <c r="I29" t="n">
         <v>133.9480626936324</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K29" t="n">
-        <v>6.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L29" t="n">
         <v>17.22</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>18.39</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H30" t="n">
-        <v>127.4</v>
+        <v>123.2</v>
       </c>
       <c r="I30" t="n">
         <v>127.1688624397354</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.35</v>
+        <v>-10.4</v>
       </c>
       <c r="L30" t="n">
-        <v>8.15</v>
+        <v>11.85</v>
       </c>
       <c r="M30" t="n">
         <v>1</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>13.8</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H31" t="n">
-        <v>115.7</v>
+        <v>147.3</v>
       </c>
       <c r="I31" t="n">
         <v>128.9224949456849</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>6.09</v>
+        <v>-19.56</v>
       </c>
       <c r="L31" t="n">
-        <v>3.73</v>
+        <v>21.92</v>
       </c>
       <c r="M31" t="n">
-        <v>0.85</v>
+        <v>9.94</v>
       </c>
       <c r="N31" t="n">
-        <v>4.91</v>
+        <v>27.31</v>
       </c>
       <c r="O31" t="n">
         <v>-3.3</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>23.72</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H32" t="n">
-        <v>142.8</v>
+        <v>134.7</v>
       </c>
       <c r="I32" t="n">
         <v>135.1969734319919</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.05</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>15.68</v>
       </c>
       <c r="M32" t="n">
-        <v>0.97</v>
+        <v>2.73</v>
       </c>
       <c r="N32" t="n">
-        <v>5.62</v>
+        <v>5.67</v>
       </c>
       <c r="O32" t="n">
         <v>27.31</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>17.96</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43717</v>
+        <v>43719</v>
       </c>
       <c r="H33" t="n">
-        <v>136.6</v>
+        <v>139.6</v>
       </c>
       <c r="I33" t="n">
         <v>137.1237960655466</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.41</v>
+        <v>-3.64</v>
       </c>
       <c r="L33" t="n">
         <v>5.27</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.43</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43887</v>
+        <v>43888</v>
       </c>
       <c r="H34" t="n">
-        <v>235.4</v>
+        <v>227</v>
       </c>
       <c r="I34" t="n">
         <v>227.5294011207281</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K34" t="n">
-        <v>68.62</v>
+        <v>62.61</v>
       </c>
       <c r="L34" t="n">
         <v>6.88</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.65</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44004</v>
+        <v>44005</v>
       </c>
       <c r="H35" t="n">
-        <v>149.9</v>
+        <v>152.4</v>
       </c>
       <c r="I35" t="n">
         <v>152.0133239828309</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K35" t="n">
-        <v>33.96</v>
+        <v>32.86</v>
       </c>
       <c r="L35" t="n">
         <v>3.13</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.56</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44363</v>
+        <v>44364</v>
       </c>
       <c r="H36" t="n">
-        <v>1404.1</v>
+        <v>1326</v>
       </c>
       <c r="I36" t="n">
         <v>1395.160562999928</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K36" t="n">
-        <v>821.33</v>
+        <v>770.08</v>
       </c>
       <c r="L36" t="n">
         <v>7.61</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>247</v>
+        <v>248</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>13</v>
+      </c>
+      <c r="U36" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>23.83</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44413</v>
+        <v>44414</v>
       </c>
       <c r="H37" t="n">
-        <v>1388.6</v>
+        <v>1489.8</v>
       </c>
       <c r="I37" t="n">
         <v>1483.424988940983</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.72</v>
+        <v>-12.35</v>
       </c>
       <c r="L37" t="n">
         <v>15.66</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>13.66</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44456</v>
+        <v>44459</v>
       </c>
       <c r="H38" t="n">
-        <v>1435.1</v>
+        <v>1375.6</v>
       </c>
       <c r="I38" t="n">
         <v>1405.942596901013</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.67</v>
+        <v>-7.67</v>
       </c>
       <c r="L38" t="n">
         <v>11.4</v>
@@ -2607,7 +3062,7 @@
         <v>1.5</v>
       </c>
       <c r="N38" t="n">
-        <v>3.14</v>
+        <v>4.15</v>
       </c>
       <c r="O38" t="n">
         <v>7.29</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>12.5</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44481</v>
+        <v>44482</v>
       </c>
       <c r="H39" t="n">
-        <v>1507</v>
+        <v>1521.8</v>
       </c>
       <c r="I39" t="n">
         <v>1518.414204706707</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.550000000000001</v>
+        <v>-10.63</v>
       </c>
       <c r="L39" t="n">
-        <v>10.61</v>
+        <v>13.35</v>
       </c>
       <c r="M39" t="n">
         <v>1.68</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44496</v>
+        <v>44497</v>
       </c>
       <c r="H40" t="n">
-        <v>1518.7</v>
+        <v>1355.9</v>
       </c>
       <c r="I40" t="n">
         <v>1422.695282070005</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.2</v>
+        <v>-10.9</v>
       </c>
       <c r="L40" t="n">
-        <v>4.82</v>
+        <v>12.87</v>
       </c>
       <c r="M40" t="n">
-        <v>0.01</v>
+        <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>3.27</v>
+        <v>10.72</v>
       </c>
       <c r="O40" t="n">
         <v>0.98</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>19.97</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44508</v>
+        <v>44509</v>
       </c>
       <c r="H41" t="n">
-        <v>1520.4</v>
+        <v>1585.5</v>
       </c>
       <c r="I41" t="n">
         <v>1579.210276182546</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>-12.13</v>
+        <v>-16.93</v>
       </c>
       <c r="L41" t="n">
-        <v>12.63</v>
+        <v>18.62</v>
       </c>
       <c r="M41" t="n">
         <v>0.87</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>13.97</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H42" t="n">
-        <v>1772.6</v>
+        <v>1663.4</v>
       </c>
       <c r="I42" t="n">
         <v>1665.047232789333</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K42" t="n">
-        <v>11.8</v>
+        <v>4.91</v>
       </c>
       <c r="L42" t="n">
         <v>4.92</v>
@@ -2835,7 +3338,7 @@
         <v>1.31</v>
       </c>
       <c r="N42" t="n">
-        <v>5.31</v>
+        <v>6.16</v>
       </c>
       <c r="O42" t="n">
         <v>4.28</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.53</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H43" t="n">
-        <v>1704.4</v>
+        <v>1764.1</v>
       </c>
       <c r="I43" t="n">
         <v>1708.330133903322</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.46</v>
+        <v>-6.05</v>
       </c>
       <c r="L43" t="n">
         <v>6.51</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.77</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44690</v>
+        <v>44691</v>
       </c>
       <c r="H44" t="n">
-        <v>2130.6</v>
+        <v>2045.1</v>
       </c>
       <c r="I44" t="n">
         <v>2078.536955910237</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K44" t="n">
-        <v>20.78</v>
+        <v>15.93</v>
       </c>
       <c r="L44" t="n">
         <v>3.28</v>
@@ -2949,7 +3476,7 @@
         <v>2.01</v>
       </c>
       <c r="N44" t="n">
-        <v>3.66</v>
+        <v>4.01</v>
       </c>
       <c r="O44" t="n">
         <v>3.5</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>13.76</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44749</v>
+        <v>44750</v>
       </c>
       <c r="H45" t="n">
-        <v>2204.9</v>
+        <v>2223.1</v>
       </c>
       <c r="I45" t="n">
         <v>2209.00043470487</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.81</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>8.789999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M45" t="n">
         <v>9.34</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44832</v>
+        <v>44833</v>
       </c>
       <c r="H46" t="n">
-        <v>3440.5</v>
+        <v>3364.8</v>
       </c>
       <c r="I46" t="n">
         <v>3377.256529231941</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K46" t="n">
-        <v>54.76</v>
+        <v>51.36</v>
       </c>
       <c r="L46" t="n">
         <v>1.27</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>14.44</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44865</v>
+        <v>44866</v>
       </c>
       <c r="H47" t="n">
-        <v>3245.3</v>
+        <v>3466.6</v>
       </c>
       <c r="I47" t="n">
         <v>3455.116977932615</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K47" t="n">
-        <v>3.55</v>
+        <v>-3.03</v>
       </c>
       <c r="L47" t="n">
         <v>5.59</v>
@@ -3120,7 +3683,7 @@
         <v>2.3</v>
       </c>
       <c r="N47" t="n">
-        <v>2.54</v>
+        <v>6.82</v>
       </c>
       <c r="O47" t="n">
         <v>-2.2</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>11.71</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H48" t="n">
-        <v>3750.5</v>
+        <v>3531.1</v>
       </c>
       <c r="I48" t="n">
         <v>3725.354808590612</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K48" t="n">
-        <v>8.19</v>
+        <v>1.86</v>
       </c>
       <c r="L48" t="n">
         <v>6.26</v>
       </c>
       <c r="M48" t="n">
-        <v>0.86</v>
+        <v>1.2</v>
       </c>
       <c r="N48" t="n">
         <v>6.32</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>13.1</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44987</v>
+        <v>44988</v>
       </c>
       <c r="H49" t="n">
-        <v>1558.2</v>
+        <v>1822.1</v>
       </c>
       <c r="I49" t="n">
         <v>1809.546680651719</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K49" t="n">
-        <v>55.87</v>
+        <v>48.4</v>
       </c>
       <c r="L49" t="n">
         <v>7.02</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>41.35</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="H50" t="n">
-        <v>2324.1</v>
+        <v>2165.4</v>
       </c>
       <c r="I50" t="n">
         <v>2190.245983492662</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K50" t="n">
-        <v>27.55</v>
+        <v>18.84</v>
       </c>
       <c r="L50" t="n">
         <v>16.31</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>15.23</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45155</v>
+        <v>45156</v>
       </c>
       <c r="H51" t="n">
-        <v>2404</v>
+        <v>2498.8</v>
       </c>
       <c r="I51" t="n">
         <v>2491.674179736676</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K51" t="n">
-        <v>-11.02</v>
+        <v>-15.4</v>
       </c>
       <c r="L51" t="n">
-        <v>15.4</v>
+        <v>19.36</v>
       </c>
       <c r="M51" t="n">
         <v>1.5</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>9.81</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45168</v>
+        <v>45169</v>
       </c>
       <c r="H52" t="n">
-        <v>2436.4</v>
+        <v>2345.4</v>
       </c>
       <c r="I52" t="n">
         <v>2373.835368254852</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.5</v>
+        <v>-6.14</v>
       </c>
       <c r="L52" t="n">
-        <v>5.14</v>
+        <v>7.52</v>
       </c>
       <c r="M52" t="n">
-        <v>0.09</v>
+        <v>2.51</v>
       </c>
       <c r="N52" t="n">
         <v>6.22</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>12.34</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45254</v>
+        <v>45258</v>
       </c>
       <c r="H53" t="n">
-        <v>2157.5</v>
+        <v>2349.5</v>
       </c>
       <c r="I53" t="n">
         <v>2268.514188698466</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="K53" t="n">
-        <v>8.01</v>
+        <v>-0.17</v>
       </c>
       <c r="L53" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>3.8</v>
+        <v>8.9</v>
       </c>
       <c r="O53" t="n">
         <v>-3.74</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.3</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H54" t="n">
-        <v>3027.2</v>
+        <v>2817.5</v>
       </c>
       <c r="I54" t="n">
         <v>3008.631285516185</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K54" t="n">
-        <v>28.84</v>
+        <v>19.92</v>
       </c>
       <c r="L54" t="n">
         <v>6.12</v>
@@ -3519,7 +4166,7 @@
         <v>1.22</v>
       </c>
       <c r="N54" t="n">
-        <v>5.35</v>
+        <v>6.93</v>
       </c>
       <c r="O54" t="n">
         <v>8.9</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>13.18</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="H55" t="n">
-        <v>2791.7</v>
+        <v>2944.9</v>
       </c>
       <c r="I55" t="n">
         <v>2937.9095088743</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K55" t="n">
-        <v>0.92</v>
+        <v>-4.52</v>
       </c>
       <c r="L55" t="n">
         <v>13.27</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>11.67</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H56" t="n">
-        <v>3534</v>
+        <v>2851.5</v>
       </c>
       <c r="I56" t="n">
         <v>3144.210357653479</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>20</v>
+        <v>-3.17</v>
       </c>
       <c r="L56" t="n">
-        <v>5.37</v>
+        <v>10</v>
       </c>
       <c r="M56" t="n">
-        <v>0.8</v>
+        <v>3.44</v>
       </c>
       <c r="N56" t="n">
-        <v>2.83</v>
+        <v>19.31</v>
       </c>
       <c r="O56" t="n">
         <v>5.49</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>28.52</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45504</v>
+        <v>45505</v>
       </c>
       <c r="H57" t="n">
-        <v>3072.7</v>
+        <v>3119.1</v>
       </c>
       <c r="I57" t="n">
         <v>3087.54641823466</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K57" t="n">
-        <v>-7.76</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L57" t="n">
         <v>19.68</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>7.71</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45541</v>
+        <v>45544</v>
       </c>
       <c r="H58" t="n">
-        <v>2884.7</v>
+        <v>2873.7</v>
       </c>
       <c r="I58" t="n">
         <v>2878.566310762259</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K58" t="n">
-        <v>-7.51</v>
+        <v>-7.87</v>
       </c>
       <c r="L58" t="n">
-        <v>8.15</v>
+        <v>9.01</v>
       </c>
       <c r="M58" t="n">
         <v>2.75</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>5.5</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45560</v>
+        <v>45561</v>
       </c>
       <c r="H59" t="n">
-        <v>3010.3</v>
+        <v>3027.4</v>
       </c>
       <c r="I59" t="n">
         <v>3018.941578955239</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.75</v>
+        <v>-5.35</v>
       </c>
       <c r="L59" t="n">
-        <v>5.39</v>
+        <v>6.2</v>
       </c>
       <c r="M59" t="n">
         <v>0.64</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.03</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45583</v>
+        <v>45586</v>
       </c>
       <c r="H60" t="n">
-        <v>2910.4</v>
+        <v>2848</v>
       </c>
       <c r="I60" t="n">
         <v>2883.012606999604</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.86</v>
+        <v>-5.93</v>
       </c>
       <c r="L60" t="n">
-        <v>4.95</v>
+        <v>6.59</v>
       </c>
       <c r="M60" t="n">
         <v>1.13</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="H61" t="n">
-        <v>2826.6</v>
+        <v>2953.3</v>
       </c>
       <c r="I61" t="n">
         <v>2939.081175985666</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K61" t="n">
-        <v>0.75</v>
+        <v>-3.7</v>
       </c>
       <c r="L61" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="M61" t="n">
         <v>0.61</v>
       </c>
       <c r="N61" t="n">
-        <v>4.24</v>
+        <v>4.48</v>
       </c>
       <c r="O61" t="n">
         <v>-2.14</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>11.48</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45615</v>
+        <v>45617</v>
       </c>
       <c r="H62" t="n">
-        <v>2735.4</v>
+        <v>2117</v>
       </c>
       <c r="I62" t="n">
         <v>2614.341547299931</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K62" t="n">
-        <v>-7.38</v>
+        <v>-28.32</v>
       </c>
       <c r="L62" t="n">
-        <v>8.300000000000001</v>
+        <v>29.26</v>
       </c>
       <c r="M62" t="n">
-        <v>0.35</v>
+        <v>10</v>
       </c>
       <c r="N62" t="n">
-        <v>2.5</v>
+        <v>22.61</v>
       </c>
       <c r="O62" t="n">
         <v>4.48</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>27.07</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H63" t="n">
-        <v>2336.4</v>
+        <v>2513.2</v>
       </c>
       <c r="I63" t="n">
         <v>2511.607168329669</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K63" t="n">
-        <v>-10.36</v>
+        <v>-18.72</v>
       </c>
       <c r="L63" t="n">
-        <v>17.14</v>
+        <v>19.53</v>
       </c>
       <c r="M63" t="n">
         <v>3.91</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>12.79</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H64" t="n">
-        <v>2301.9</v>
+        <v>2157.3</v>
       </c>
       <c r="I64" t="n">
         <v>2263.624636616627</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K64" t="n">
-        <v>-8.41</v>
+        <v>-14.16</v>
       </c>
       <c r="L64" t="n">
-        <v>8.640000000000001</v>
+        <v>14.48</v>
       </c>
       <c r="M64" t="n">
         <v>0.68</v>
       </c>
       <c r="N64" t="n">
-        <v>4.18</v>
+        <v>6.28</v>
       </c>
       <c r="O64" t="n">
         <v>7.57</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>14.74</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H65" t="n">
-        <v>2184</v>
+        <v>2238.1</v>
       </c>
       <c r="I65" t="n">
         <v>2236.032811797522</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.24</v>
+        <v>-3.75</v>
       </c>
       <c r="L65" t="n">
         <v>15.5</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>10.37</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45826</v>
+        <v>45827</v>
       </c>
       <c r="H66" t="n">
-        <v>2384.1</v>
+        <v>2346.7</v>
       </c>
       <c r="I66" t="n">
         <v>2358.38652875969</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K66" t="n">
-        <v>6.52</v>
+        <v>4.85</v>
       </c>
       <c r="L66" t="n">
         <v>7.09</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="H67" t="n">
-        <v>2507.3</v>
+        <v>2565.5</v>
       </c>
       <c r="I67" t="n">
         <v>2552.202916886731</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.84</v>
+        <v>-9.32</v>
       </c>
       <c r="L67" t="n">
-        <v>7.15</v>
+        <v>10.79</v>
       </c>
       <c r="M67" t="n">
         <v>1.29</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="H68" t="n">
-        <v>2455.6</v>
+        <v>2356.5</v>
       </c>
       <c r="I68" t="n">
         <v>2419.264879512507</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.28</v>
+        <v>-8.15</v>
       </c>
       <c r="L68" t="n">
-        <v>5.24</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M68" t="n">
-        <v>0.23</v>
+        <v>0.91</v>
       </c>
       <c r="N68" t="n">
-        <v>2.23</v>
+        <v>4.04</v>
       </c>
       <c r="O68" t="n">
         <v>2.32</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>8.17</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="H69" t="n">
-        <v>2328.7</v>
+        <v>2447</v>
       </c>
       <c r="I69" t="n">
         <v>2330.056629379691</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K69" t="n">
-        <v>1.18</v>
+        <v>-3.84</v>
       </c>
       <c r="L69" t="n">
-        <v>3.67</v>
+        <v>6.1</v>
       </c>
       <c r="M69" t="n">
-        <v>1.23</v>
+        <v>3.87</v>
       </c>
       <c r="N69" t="n">
-        <v>4.84</v>
+        <v>5.08</v>
       </c>
       <c r="O69" t="n">
         <v>-4.04</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>6.86</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H70" t="n">
-        <v>2391.7</v>
+        <v>2346</v>
       </c>
       <c r="I70" t="n">
         <v>2366.082753256437</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.26</v>
+        <v>-4.13</v>
       </c>
       <c r="L70" t="n">
-        <v>2.64</v>
+        <v>5.28</v>
       </c>
       <c r="M70" t="n">
         <v>0.86</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>7.99</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H71" t="n">
-        <v>1995.4</v>
+        <v>2202.6</v>
       </c>
       <c r="I71" t="n">
         <v>2159.359112433457</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K71" t="n">
-        <v>14.94</v>
+        <v>6.11</v>
       </c>
       <c r="L71" t="n">
         <v>5.66</v>
       </c>
       <c r="M71" t="n">
-        <v>2.4</v>
+        <v>7.75</v>
       </c>
       <c r="N71" t="n">
-        <v>5.11</v>
+        <v>10.38</v>
       </c>
       <c r="O71" t="n">
         <v>-1.91</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>13.04</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H72" t="n">
-        <v>2039.9</v>
+        <v>1999.2</v>
       </c>
       <c r="I72" t="n">
         <v>2039.609649834627</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K72" t="n">
-        <v>-7.39</v>
+        <v>-9.23</v>
       </c>
       <c r="L72" t="n">
-        <v>7.83</v>
+        <v>11.9</v>
       </c>
       <c r="M72" t="n">
         <v>3.18</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>8.82</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H73" t="n">
-        <v>1882.1</v>
+        <v>2043.8</v>
       </c>
       <c r="I73" t="n">
         <v>2010.354738638773</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K73" t="n">
-        <v>5.86</v>
+        <v>-2.23</v>
       </c>
       <c r="L73" t="n">
-        <v>1.54</v>
+        <v>4.99</v>
       </c>
       <c r="M73" t="n">
-        <v>3.76</v>
+        <v>6.26</v>
       </c>
       <c r="N73" t="n">
-        <v>4.76</v>
+        <v>8.59</v>
       </c>
       <c r="O73" t="n">
         <v>-2</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>13.37</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="H74" t="n">
-        <v>2985.7</v>
+        <v>2964.9</v>
       </c>
       <c r="I74" t="n">
         <v>2969.408840407462</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K74" t="n">
-        <v>46.09</v>
+        <v>45.07</v>
       </c>
       <c r="L74" t="n">
         <v>3.36</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>5</v>
+      </c>
+      <c r="U74" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>7.18</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="H75" t="n">
-        <v>3112</v>
+        <v>3169</v>
       </c>
       <c r="I75" t="n">
         <v>3161.832493938948</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K75" t="n">
-        <v>-4.96</v>
+        <v>-6.88</v>
       </c>
       <c r="L75" t="n">
-        <v>6.75</v>
+        <v>6.88</v>
       </c>
       <c r="M75" t="n">
         <v>0.46</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>6.8</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H76" t="n">
-        <v>3168.5</v>
+        <v>2859.1</v>
       </c>
       <c r="I76" t="n">
         <v>2967.154815726657</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.02</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>1.39</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="N76" t="n">
-        <v>0.02</v>
+        <v>9.76</v>
       </c>
       <c r="O76" t="n">
         <v>1.83</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>40</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9791,7 +10722,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.1</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="6">
@@ -9801,7 +10732,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -9811,7 +10742,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8">
@@ -9821,7 +10752,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9831,7 +10762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64.5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -9841,7 +10772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108.6</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="11">
@@ -9851,7 +10782,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -9861,7 +10792,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -9871,7 +10802,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="14">
@@ -9881,7 +10812,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19.21</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="15">
@@ -9891,7 +10822,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34.34</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="16">
@@ -9901,7 +10832,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.67</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="17">
@@ -9911,7 +10842,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>821.33</v>
+        <v>770.08</v>
       </c>
     </row>
     <row r="18">
@@ -9921,7 +10852,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
@@ -9931,7 +10862,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10.01</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -9941,7 +10872,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.75</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -9961,7 +10892,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -9971,7 +10902,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -9981,7 +10912,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5.3</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="25">
@@ -10001,7 +10932,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.6</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="27">
@@ -10011,7 +10942,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.04</v>
+        <v>27.31</v>
       </c>
     </row>
     <row r="28">
@@ -10021,7 +10952,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
